--- a/data/trans_camb/P16A07-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A07-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,55</t>
+          <t>-1,06; 5,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 3,06</t>
+          <t>-1,92; 3,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 1,09</t>
+          <t>-3,08; 1,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 4,4</t>
+          <t>-5,29; 3,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 5,29</t>
+          <t>-4,18; 4,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 0,42</t>
+          <t>-7,75; 0,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,04</t>
+          <t>-2,4; 3,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 3,34</t>
+          <t>-2,17; 3,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; -0,11</t>
+          <t>-4,38; -0,13</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 348,23</t>
+          <t>-38,45; 482,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 269,61</t>
+          <t>-60,56; 315,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-87,21; 132,59</t>
+          <t>-83,99; 124,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-50,32; 75,72</t>
+          <t>-49,17; 76,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,78; 96,17</t>
+          <t>-43,05; 86,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,5; 8,3</t>
+          <t>-68,83; 6,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,21; 82,36</t>
+          <t>-35,97; 84,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-36,05; 84,31</t>
+          <t>-32,73; 82,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-65,71; -1,43</t>
+          <t>-64,29; -0,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 4,15</t>
+          <t>0,04; 3,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 2,16</t>
+          <t>-0,58; 2,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,37</t>
+          <t>1,01; 5,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 5,35</t>
+          <t>-0,93; 5,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 3,56</t>
+          <t>-2,46; 3,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 6,93</t>
+          <t>0,75; 6,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 4,24</t>
+          <t>0,34; 4,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 2,35</t>
+          <t>-0,96; 2,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,37</t>
+          <t>1,69; 5,15</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,13; 1232,33</t>
+          <t>-31,4; 1324,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,69; 784,14</t>
+          <t>-57,31; 824,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55,39; 1758,39</t>
+          <t>42,7; 1806,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,65; 112,48</t>
+          <t>-15,19; 126,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,9; 83,29</t>
+          <t>-33,19; 80,83</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 165,5</t>
+          <t>10,51; 160,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 173,9</t>
+          <t>5,58; 161,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,14; 90,65</t>
+          <t>-24,72; 90,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>42,37; 209,45</t>
+          <t>38,53; 205,71</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,81</t>
+          <t>0,41; 5,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 0,85</t>
+          <t>-2,47; 0,85</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,42; 7,0</t>
+          <t>1,68; 6,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,52</t>
+          <t>0,4; 8,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 3,02</t>
+          <t>-3,4; 2,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,56; 8,36</t>
+          <t>1,75; 8,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,37</t>
+          <t>1,51; 6,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 1,35</t>
+          <t>-2,25; 1,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,95</t>
+          <t>2,74; 7,07</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-23,84; 1389,38</t>
+          <t>-18,57; 1265,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,01; 1850,81</t>
+          <t>30,69; 1601,18</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15,91; 303,92</t>
+          <t>1,69; 283,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,98; 103,27</t>
+          <t>-55,84; 102,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,16; 275,95</t>
+          <t>22,65; 299,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,95; 298,9</t>
+          <t>37,38; 298,22</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-57,55; 79,05</t>
+          <t>-58,68; 72,36</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53,32; 340,07</t>
+          <t>65,86; 356,59</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,29</t>
+          <t>-0,83; 2,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 2,86</t>
+          <t>-0,54; 2,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 7,91</t>
+          <t>1,57; 7,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 9,17</t>
+          <t>2,32; 9,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 5,68</t>
+          <t>-0,58; 6,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 2,52</t>
+          <t>-3,15; 2,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 5,07</t>
+          <t>1,24; 5,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,88</t>
+          <t>-0,1; 3,85</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 4,06</t>
+          <t>-0,07; 3,8</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-86,23; 951,41</t>
+          <t>-75,53; 910,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-62,77; 998,4</t>
+          <t>-61,42; inf</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,98; 2561,34</t>
+          <t>29,19; 2292,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,02; 294,69</t>
+          <t>33,61; 307,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,8; 177,9</t>
+          <t>-15,51; 213,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-52,23; 84,71</t>
+          <t>-50,61; 84,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,17; 270,11</t>
+          <t>31,48; 288,68</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 195,58</t>
+          <t>-5,35; 197,58</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 204,37</t>
+          <t>-5,94; 184,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 2,07</t>
+          <t>-5,08; 2,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 5,29</t>
+          <t>-2,84; 5,36</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,4; -0,32</t>
+          <t>-6,43; -0,59</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 10,57</t>
+          <t>-2,06; 10,84</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 3,33</t>
+          <t>-8,64; 3,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,78; -1,92</t>
+          <t>-11,89; -1,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 4,9</t>
+          <t>-2,42; 5,4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 2,84</t>
+          <t>-4,29; 3,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,68; -1,77</t>
+          <t>-7,87; -2,0</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-81,18; 100,73</t>
+          <t>-80,83; 99,0</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-47,65; 200,89</t>
+          <t>-45,45; 218,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-92,27; 8,75</t>
+          <t>-93,23; -2,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,84; 127,31</t>
+          <t>-15,27; 138,01</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-57,27; 44,11</t>
+          <t>-57,56; 53,94</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-74,43; -22,28</t>
+          <t>-74,8; -21,85</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-27,33; 77,8</t>
+          <t>-25,13; 93,44</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 43,93</t>
+          <t>-44,19; 56,66</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-74,09; -31,26</t>
+          <t>-74,86; -32,29</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,95</t>
+          <t>0,69; 5,64</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 1,84</t>
+          <t>-1,24; 1,82</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,9</t>
+          <t>1,92; 6,98</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,53; 9,26</t>
+          <t>1,56; 9,54</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,5; 9,56</t>
+          <t>1,94; 9,46</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 5,81</t>
+          <t>0,12; 6,07</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,95; 6,66</t>
+          <t>2,1; 7,06</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,1</t>
+          <t>0,88; 5,52</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,5</t>
+          <t>1,7; 5,68</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-42,48; —</t>
+          <t>-25,21; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>47,39; —</t>
+          <t>55,05; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>18,88; 496,24</t>
+          <t>20,85; 461,03</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>21,15; 536,2</t>
+          <t>32,73; 548,7</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 339,32</t>
+          <t>-4,07; 322,0</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>60,42; 585,28</t>
+          <t>57,3; 589,27</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>15,68; 408,19</t>
+          <t>22,81; 469,17</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>45,17; 500,19</t>
+          <t>50,72; 501,79</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,34</t>
+          <t>0,48; 4,66</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,06</t>
+          <t>-1,92; 1,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,48</t>
+          <t>0,67; 4,48</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 2,63</t>
+          <t>-3,18; 2,76</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 0,41</t>
+          <t>-4,75; 0,66</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 3,0</t>
+          <t>-5,63; 3,35</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 2,91</t>
+          <t>-0,64; 2,89</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 0,24</t>
+          <t>-2,9; 0,38</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,17</t>
+          <t>-1,3; 3,19</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0,41; 321,33</t>
+          <t>10,19; 372,7</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-72,1; 93,27</t>
+          <t>-72,18; 109,49</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14,36; 362,54</t>
+          <t>17,51; 360,06</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-33,94; 44,86</t>
+          <t>-36,04; 47,0</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-55,85; 6,33</t>
+          <t>-53,4; 11,69</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-54,31; 46,15</t>
+          <t>-58,06; 50,64</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 75,7</t>
+          <t>-11,79; 73,04</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-53,24; 7,59</t>
+          <t>-53,09; 8,27</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 76,72</t>
+          <t>-22,95; 77,38</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,41</t>
+          <t>-3,43; 0,65</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 0,93</t>
+          <t>-2,83; 1,1</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,51; -1,12</t>
+          <t>-4,43; -0,99</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 2,06</t>
+          <t>-3,03; 2,28</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 4,66</t>
+          <t>-1,1; 4,44</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,2</t>
+          <t>-1,57; 3,17</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,71</t>
+          <t>-2,51; 0,72</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 2,09</t>
+          <t>-1,38; 2,33</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 0,33</t>
+          <t>-3,55; 0,21</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-63,06; 18,32</t>
+          <t>-66,11; 26,14</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-53,1; 30,89</t>
+          <t>-54,75; 39,41</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-88,81; -37,52</t>
+          <t>-87,35; -32,82</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-36,57; 35,79</t>
+          <t>-35,61; 40,84</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-14,97; 79,91</t>
+          <t>-15,86; 78,27</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-19,59; 56,72</t>
+          <t>-18,93; 54,47</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-38,54; 14,46</t>
+          <t>-39,45; 17,1</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 42,71</t>
+          <t>-20,92; 49,66</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-51,62; 6,28</t>
+          <t>-55,46; 3,76</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,93</t>
+          <t>0,24; 1,87</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,68</t>
+          <t>-0,59; 0,81</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,88</t>
+          <t>0,26; 1,95</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,07</t>
+          <t>0,67; 3,26</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 1,77</t>
+          <t>-0,56; 1,98</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,85</t>
+          <t>-0,9; 1,87</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,31</t>
+          <t>0,71; 2,21</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,09</t>
+          <t>-0,36; 1,05</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,71</t>
+          <t>0,1; 1,67</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>5,48; 102,5</t>
+          <t>9,23; 105,17</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-27,8; 37,1</t>
+          <t>-24,77; 44,99</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>7,85; 104,67</t>
+          <t>9,6; 110,28</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>6,83; 52,1</t>
+          <t>9,15; 56,31</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 29,55</t>
+          <t>-7,99; 32,64</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-12,63; 31,16</t>
+          <t>-12,2; 31,9</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>14,21; 57,59</t>
+          <t>15,34; 56,44</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 27,41</t>
+          <t>-8,22; 26,14</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2,42; 43,0</t>
+          <t>2,14; 41,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A07-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P16A07-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,9</t>
+          <t>-1,05</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-3,58</t>
+          <t>-3,64</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,23</t>
+          <t>-2,28</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 5,04</t>
+          <t>-1,39; 4,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 3,54</t>
+          <t>-2,19; 3,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 1,05</t>
+          <t>-3,48; 0,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 3,92</t>
+          <t>-5,73; 3,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 4,92</t>
+          <t>-5,01; 5,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-7,75; 0,19</t>
+          <t>-7,59; -0,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 3,15</t>
+          <t>-2,38; 3,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 3,14</t>
+          <t>-2,19; 3,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,38; -0,13</t>
+          <t>-4,6; -0,24</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-37,46%</t>
+          <t>-43,52%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-43,74%</t>
+          <t>-44,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-42,67%</t>
+          <t>-43,64%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-38,45; 482,05</t>
+          <t>-46,4; 395,46</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-60,56; 315,39</t>
+          <t>-64,53; 273,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-83,99; 124,67</t>
+          <t>-86,6; 104,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,17; 76,24</t>
+          <t>-51,21; 69,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,05; 86,39</t>
+          <t>-44,19; 86,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-68,83; 6,39</t>
+          <t>-67,12; 2,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 84,96</t>
+          <t>-35,58; 84,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,73; 82,86</t>
+          <t>-32,99; 95,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-64,29; -0,6</t>
+          <t>-65,89; -4,48</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,95</t>
+          <t>3,65</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>3,3</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,04; 3,89</t>
+          <t>-0,05; 3,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 2,13</t>
+          <t>-0,59; 2,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,24</t>
+          <t>1,11; 5,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 5,63</t>
+          <t>-0,63; 5,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 3,48</t>
+          <t>-2,59; 3,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,91</t>
+          <t>0,7; 6,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,12</t>
+          <t>0,23; 4,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 2,37</t>
+          <t>-1,01; 2,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,15</t>
+          <t>1,54; 5,07</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>364,67%</t>
+          <t>363,31%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>101,11%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,4; 1324,12</t>
+          <t>-28,51; 1492,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-57,31; 824,21</t>
+          <t>-61,33; 826,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42,7; 1806,9</t>
+          <t>43,64; 1846,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-15,19; 126,16</t>
+          <t>-9,17; 125,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 80,83</t>
+          <t>-35,01; 75,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,51; 160,19</t>
+          <t>7,66; 143,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,58; 161,39</t>
+          <t>3,51; 176,82</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 90,04</t>
+          <t>-25,4; 97,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,53; 205,71</t>
+          <t>33,8; 198,78</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4,13</t>
+          <t>4,51</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>5,18</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>4,7</t>
+          <t>4,92</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,82</t>
+          <t>0,44; 5,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,85</t>
+          <t>-2,62; 0,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,85</t>
+          <t>2,03; 7,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 8,44</t>
+          <t>0,61; 8,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 2,96</t>
+          <t>-3,34; 3,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 8,53</t>
+          <t>1,65; 8,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 6,0</t>
+          <t>1,29; 5,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,39</t>
+          <t>-2,25; 1,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 7,07</t>
+          <t>2,89; 7,02</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>349,55%</t>
+          <t>381,25%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>113,03%</t>
+          <t>114,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>161,89%</t>
+          <t>169,78%</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 1265,86</t>
+          <t>-21,48; 1390,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1225,37 +1225,37 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>30,69; 1601,18</t>
+          <t>33,57; 1894,06</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,69; 283,11</t>
+          <t>7,15; 275,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-55,84; 102,58</t>
+          <t>-58,54; 99,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,65; 299,88</t>
+          <t>24,83; 299,81</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,38; 298,22</t>
+          <t>30,76; 287,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-58,68; 72,36</t>
+          <t>-58,68; 77,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65,86; 356,59</t>
+          <t>66,21; 349,1</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3,89</t>
+          <t>3,47</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>0,88</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>2,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,21</t>
+          <t>-0,8; 2,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,72</t>
+          <t>-0,62; 2,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,57; 7,37</t>
+          <t>1,29; 6,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,32; 9,22</t>
+          <t>2,0; 9,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 6,19</t>
+          <t>-0,71; 6,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 2,45</t>
+          <t>-1,74; 3,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,43</t>
+          <t>1,26; 5,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 3,85</t>
+          <t>0,09; 3,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,8</t>
+          <t>0,45; 4,29</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>487,43%</t>
+          <t>434,86%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-2,88%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>81,3%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-75,53; 910,01</t>
+          <t>-94,59; —</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-61,42; inf</t>
+          <t>-66,84; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29,19; 2292,47</t>
+          <t>34,23; 2646,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,61; 307,06</t>
+          <t>29,48; 312,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 213,09</t>
+          <t>-13,45; 218,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,61; 84,16</t>
+          <t>-30,82; 124,67</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,48; 288,68</t>
+          <t>28,08; 266,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 197,58</t>
+          <t>-0,63; 196,42</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 184,84</t>
+          <t>11,14; 227,33</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-3,17</t>
+          <t>-3,28</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-6,22</t>
+          <t>-6,44</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,58</t>
+          <t>-4,8</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 2,14</t>
+          <t>-4,95; 2,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 5,36</t>
+          <t>-2,86; 5,52</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,43; -0,59</t>
+          <t>-6,55; -0,7</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 10,84</t>
+          <t>-2,94; 10,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 3,63</t>
+          <t>-8,03; 3,63</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,89; -1,79</t>
+          <t>-11,67; -1,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 5,4</t>
+          <t>-2,92; 4,99</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 3,07</t>
+          <t>-4,65; 2,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,87; -2,0</t>
+          <t>-7,67; -2,25</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-71,54%</t>
+          <t>-74,09%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-54,54%</t>
+          <t>-56,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-57,58%</t>
+          <t>-60,39%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-80,83; 99,0</t>
+          <t>-78,32; 98,53</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-45,45; 218,42</t>
+          <t>-49,02; 231,07</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-93,23; -2,93</t>
+          <t>-94,89; -15,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 138,01</t>
+          <t>-21,0; 123,2</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-57,56; 53,94</t>
+          <t>-56,45; 46,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-74,8; -21,85</t>
+          <t>-75,06; -23,74</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-25,13; 93,44</t>
+          <t>-27,77; 85,26</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-44,19; 56,66</t>
+          <t>-45,55; 45,95</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-74,86; -32,29</t>
+          <t>-74,44; -33,17</t>
         </is>
       </c>
     </row>
@@ -1714,29 +1714,29 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>4,08</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>5,53</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>5,26</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2,94</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
           <t>4,24</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>5,53</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>5,26</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>3,03</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>4,24</t>
-        </is>
-      </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
           <t>2,83</t>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>3,48</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,64</t>
+          <t>0,75; 6,01</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,82</t>
+          <t>-1,15; 2,21</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,98</t>
+          <t>1,83; 6,92</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,56; 9,54</t>
+          <t>1,72; 9,67</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,46</t>
+          <t>1,48; 9,45</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,12; 6,07</t>
+          <t>-0,39; 5,68</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,06</t>
+          <t>1,96; 6,64</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,52</t>
+          <t>0,53; 5,1</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,7; 5,68</t>
+          <t>1,49; 5,3</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>557,4%</t>
+          <t>535,73%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>178,73%</t>
+          <t>172,8%</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-25,21; —</t>
+          <t>12,62; —</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>55,05; —</t>
+          <t>52,9; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>20,85; 461,03</t>
+          <t>22,96; 523,32</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>32,73; 548,7</t>
+          <t>29,13; 550,13</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 322,0</t>
+          <t>-12,26; 300,78</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57,3; 589,27</t>
+          <t>59,97; 515,66</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>22,81; 469,17</t>
+          <t>9,53; 368,06</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>50,72; 501,79</t>
+          <t>40,71; 436,23</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2,47</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>1,68</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>2,18</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,66</t>
+          <t>0,47; 4,48</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 1,0</t>
+          <t>-1,92; 1,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,48</t>
+          <t>0,81; 4,66</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 2,76</t>
+          <t>-2,91; 2,59</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 0,66</t>
+          <t>-4,73; 0,67</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 3,35</t>
+          <t>-1,0; 4,61</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,89</t>
+          <t>-0,73; 2,91</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 0,38</t>
+          <t>-2,98; 0,2</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 3,19</t>
+          <t>0,45; 3,94</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>126,86%</t>
+          <t>134,8%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-4,0%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>45,95%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>10,19; 372,7</t>
+          <t>18,3; 378,33</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-72,18; 109,49</t>
+          <t>-71,83; 102,62</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>17,51; 360,06</t>
+          <t>17,8; 371,27</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-36,04; 47,0</t>
+          <t>-33,51; 43,48</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-53,4; 11,69</t>
+          <t>-54,02; 12,82</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-58,06; 50,64</t>
+          <t>-12,22; 75,88</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 73,04</t>
+          <t>-13,81; 74,22</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-53,09; 8,27</t>
+          <t>-51,77; 6,15</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-22,95; 77,38</t>
+          <t>6,87; 99,96</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,62</t>
+          <t>-2,09</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,84</t>
+          <t>0,75</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,35</t>
+          <t>-0,65</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 0,65</t>
+          <t>-3,28; 0,6</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,1</t>
+          <t>-2,75; 1,01</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,43; -0,99</t>
+          <t>-3,87; -0,43</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 2,28</t>
+          <t>-2,95; 2,37</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 4,44</t>
+          <t>-1,06; 4,56</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,17</t>
+          <t>-2,0; 3,17</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,72</t>
+          <t>-2,33; 0,74</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 2,33</t>
+          <t>-1,19; 2,15</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 0,21</t>
+          <t>-2,23; 0,72</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-65,16%</t>
+          <t>-51,84%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-24,28%</t>
+          <t>-11,7%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-66,11; 26,14</t>
+          <t>-62,88; 21,29</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-54,75; 39,41</t>
+          <t>-53,4; 34,68</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-87,35; -32,82</t>
+          <t>-74,19; -9,86</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-35,61; 40,84</t>
+          <t>-34,42; 44,5</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 78,27</t>
+          <t>-12,8; 77,53</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 54,47</t>
+          <t>-23,72; 57,72</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-39,45; 17,1</t>
+          <t>-37,99; 14,93</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 49,66</t>
+          <t>-19,36; 45,96</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-55,46; 3,76</t>
+          <t>-34,96; 14,9</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,31</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,29</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,87</t>
+          <t>0,16; 1,83</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,81</t>
+          <t>-0,63; 0,75</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,95</t>
+          <t>0,48; 2,13</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,26</t>
+          <t>0,64; 3,25</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,98</t>
+          <t>-0,59; 1,9</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,87</t>
+          <t>0,01; 2,37</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,21</t>
+          <t>0,67; 2,19</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,05</t>
+          <t>-0,27; 1,17</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,67</t>
+          <t>0,58; 1,89</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>51,0%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>9,23; 105,17</t>
+          <t>4,37; 99,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-24,77; 44,99</t>
+          <t>-26,38; 43,5</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>9,6; 110,28</t>
+          <t>17,06; 113,62</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>9,15; 56,31</t>
+          <t>8,78; 55,49</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 32,64</t>
+          <t>-8,42; 32,59</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 31,9</t>
+          <t>0,31; 41,59</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>15,34; 56,44</t>
+          <t>14,81; 56,27</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 26,14</t>
+          <t>-5,81; 29,43</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>2,14; 41,75</t>
+          <t>11,7; 46,62</t>
         </is>
       </c>
     </row>
